--- a/AAII_Financials/Quarterly/SAIL_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SAIL_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="302" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="315" uniqueCount="92">
   <si>
     <t>SAIL</t>
   </si>
@@ -656,187 +656,212 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A5:N102"/>
+  <dimension ref="A5:P102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="14" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="16" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46234</v>
+      </c>
+      <c r="E7" s="2">
+        <v>46142</v>
+      </c>
+      <c r="F7" s="2">
         <v>46053</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45961</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45869</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45777</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45688</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45596</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>45504</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>45412</v>
       </c>
-      <c r="L7" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="M7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="N7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="P7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>308800</v>
+      </c>
+      <c r="E8" s="3">
+        <v>280100</v>
+      </c>
+      <c r="F8" s="3">
         <v>294600</v>
       </c>
-      <c r="E8" s="3">
+      <c r="G8" s="3">
         <v>281900</v>
       </c>
-      <c r="F8" s="3">
+      <c r="H8" s="3">
         <v>264400</v>
       </c>
-      <c r="G8" s="3">
+      <c r="I8" s="3">
         <v>230500</v>
       </c>
-      <c r="H8" s="3">
+      <c r="J8" s="3">
         <v>240100</v>
       </c>
-      <c r="I8" s="3">
+      <c r="K8" s="3">
         <v>235300</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>198600</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>187700</v>
       </c>
-      <c r="L8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
-        <v>96900</v>
+        <v>102400</v>
       </c>
       <c r="E9" s="3">
-        <v>94700</v>
+        <v>98800</v>
       </c>
       <c r="F9" s="3">
+        <v>97300</v>
+      </c>
+      <c r="G9" s="3">
+        <v>94600</v>
+      </c>
+      <c r="H9" s="3">
         <v>86600</v>
       </c>
-      <c r="G9" s="3">
-        <v>102500</v>
-      </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
+        <v>102200</v>
+      </c>
+      <c r="J9" s="3">
         <v>80300</v>
       </c>
-      <c r="I9" s="3">
+      <c r="K9" s="3">
         <v>78000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="L9" s="3">
         <v>75300</v>
       </c>
-      <c r="K9" s="3">
+      <c r="M9" s="3">
         <v>72200</v>
       </c>
-      <c r="L9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>197800</v>
+        <v>206400</v>
       </c>
       <c r="E10" s="3">
-        <v>187200</v>
+        <v>181400</v>
       </c>
       <c r="F10" s="3">
+        <v>197400</v>
+      </c>
+      <c r="G10" s="3">
+        <v>187300</v>
+      </c>
+      <c r="H10" s="3">
         <v>177800</v>
       </c>
-      <c r="G10" s="3">
-        <v>128000</v>
-      </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
+        <v>128300</v>
+      </c>
+      <c r="J10" s="3">
         <v>159800</v>
       </c>
-      <c r="I10" s="3">
+      <c r="K10" s="3">
         <v>157300</v>
       </c>
-      <c r="J10" s="3">
+      <c r="L10" s="3">
         <v>123300</v>
       </c>
-      <c r="K10" s="3">
+      <c r="M10" s="3">
         <v>115500</v>
       </c>
-      <c r="L10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -851,46 +876,54 @@
       <c r="L11" s="3"/>
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O11" s="3"/>
+      <c r="P11" s="3"/>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>62200</v>
+      </c>
+      <c r="E12" s="3">
+        <v>61700</v>
+      </c>
+      <c r="F12" s="3">
         <v>56400</v>
       </c>
-      <c r="E12" s="3">
+      <c r="G12" s="3">
         <v>51200</v>
       </c>
-      <c r="F12" s="3">
+      <c r="H12" s="3">
         <v>48100</v>
       </c>
-      <c r="G12" s="3">
+      <c r="I12" s="3">
         <v>67300</v>
       </c>
-      <c r="H12" s="3">
+      <c r="J12" s="3">
         <v>45500</v>
       </c>
-      <c r="I12" s="3">
+      <c r="K12" s="3">
         <v>39200</v>
       </c>
-      <c r="J12" s="3">
+      <c r="L12" s="3">
         <v>43100</v>
       </c>
-      <c r="K12" s="3">
+      <c r="M12" s="3">
         <v>41900</v>
       </c>
-      <c r="L12" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -927,26 +960,32 @@
       <c r="N13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O13" s="3">
+        <v>0</v>
+      </c>
+      <c r="P13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>0</v>
+        <v>800</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>3</v>
       </c>
       <c r="F14" s="3">
+        <v>0</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H14" s="3">
         <v>1600</v>
       </c>
-      <c r="G14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I14" s="3" t="s">
         <v>3</v>
       </c>
@@ -965,46 +1004,58 @@
       <c r="N14" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>52900</v>
+        <v>52600</v>
       </c>
       <c r="E15" s="3">
         <v>52400</v>
       </c>
       <c r="F15" s="3">
+        <v>52900</v>
+      </c>
+      <c r="G15" s="3">
+        <v>52400</v>
+      </c>
+      <c r="H15" s="3">
         <v>52100</v>
       </c>
-      <c r="G15" s="3">
+      <c r="I15" s="3">
         <v>51800</v>
       </c>
-      <c r="H15" s="3">
+      <c r="J15" s="3">
         <v>51200</v>
       </c>
-      <c r="I15" s="3">
+      <c r="K15" s="3">
         <v>53500</v>
       </c>
-      <c r="J15" s="3">
+      <c r="L15" s="3">
         <v>66100</v>
       </c>
-      <c r="K15" s="3">
+      <c r="M15" s="3">
         <v>66000</v>
       </c>
-      <c r="L15" s="3">
-        <v>0</v>
-      </c>
-      <c r="M15" s="3">
-        <v>0</v>
-      </c>
       <c r="N15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O15" s="3">
+        <v>0</v>
+      </c>
+      <c r="P15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1016,84 +1067,98 @@
       <c r="L16" s="3"/>
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
-    </row>
-    <row r="17" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O16" s="3"/>
+      <c r="P16" s="3"/>
+    </row>
+    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>367000</v>
+      </c>
+      <c r="E17" s="3">
+        <v>360000</v>
+      </c>
+      <c r="F17" s="3">
         <v>334700</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>323600</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>303500</v>
       </c>
-      <c r="G17" s="3">
+      <c r="I17" s="3">
         <v>415400</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>270300</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>259800</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>264400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>255800</v>
       </c>
-      <c r="L17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-58200</v>
+      </c>
+      <c r="E18" s="3">
+        <v>-79800</v>
+      </c>
+      <c r="F18" s="3">
         <v>-40100</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>-41600</v>
       </c>
-      <c r="F18" s="3">
+      <c r="H18" s="3">
         <v>-39200</v>
       </c>
-      <c r="G18" s="3">
+      <c r="I18" s="3">
         <v>-185000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="J18" s="3">
         <v>-30200</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>-24500</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>-65800</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>-68200</v>
       </c>
-      <c r="L18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1108,8 +1173,10 @@
       <c r="L19" s="3"/>
       <c r="M19" s="3"/>
       <c r="N19" s="3"/>
-    </row>
-    <row r="20" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O19" s="3"/>
+      <c r="P19" s="3"/>
+    </row>
+    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1117,75 +1184,87 @@
         <v>1300</v>
       </c>
       <c r="E20" s="3">
+        <v>3000</v>
+      </c>
+      <c r="F20" s="3">
+        <v>1300</v>
+      </c>
+      <c r="G20" s="3">
         <v>1400</v>
       </c>
-      <c r="F20" s="3">
+      <c r="H20" s="3">
         <v>1700</v>
       </c>
-      <c r="G20" s="3">
+      <c r="I20" s="3">
         <v>200</v>
       </c>
-      <c r="H20" s="3">
+      <c r="J20" s="3">
         <v>2200</v>
       </c>
-      <c r="I20" s="3">
+      <c r="K20" s="3">
         <v>900</v>
       </c>
-      <c r="J20" s="3">
+      <c r="L20" s="3">
         <v>1100</v>
       </c>
-      <c r="K20" s="3">
+      <c r="M20" s="3">
         <v>1200</v>
       </c>
-      <c r="L20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-6900</v>
+      </c>
+      <c r="E21" s="3">
+        <v>-30400</v>
+      </c>
+      <c r="F21" s="3">
         <v>11400</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
         <v>9300</v>
       </c>
-      <c r="F21" s="3">
+      <c r="H21" s="3">
         <v>11200</v>
       </c>
-      <c r="G21" s="3">
+      <c r="I21" s="3">
         <v>-133400</v>
       </c>
-      <c r="H21" s="3">
+      <c r="J21" s="3">
         <v>18800</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>28200</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>-900</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>-3400</v>
       </c>
-      <c r="L21" s="3">
-        <v>0</v>
-      </c>
-      <c r="M21" s="3">
-        <v>0</v>
-      </c>
       <c r="N21" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="22" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O21" s="3">
+        <v>0</v>
+      </c>
+      <c r="P21" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1196,110 +1275,128 @@
         <v>300</v>
       </c>
       <c r="F22" s="3">
+        <v>300</v>
+      </c>
+      <c r="G22" s="3">
+        <v>300</v>
+      </c>
+      <c r="H22" s="3">
         <v>1700</v>
       </c>
-      <c r="G22" s="3">
+      <c r="I22" s="3">
         <v>22400</v>
       </c>
-      <c r="H22" s="3">
+      <c r="J22" s="3">
         <v>46500</v>
       </c>
-      <c r="I22" s="3">
+      <c r="K22" s="3">
         <v>46600</v>
       </c>
-      <c r="J22" s="3">
+      <c r="L22" s="3">
         <v>47300</v>
       </c>
-      <c r="K22" s="3">
+      <c r="M22" s="3">
         <v>46200</v>
       </c>
-      <c r="L22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-57100</v>
+      </c>
+      <c r="E23" s="3">
+        <v>-80000</v>
+      </c>
+      <c r="F23" s="3">
         <v>-39000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>-40800</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>-41900</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>-204300</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>-78400</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>-71400</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>-113200</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>-113600</v>
       </c>
-      <c r="L23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-6800</v>
+      </c>
+      <c r="E24" s="3">
+        <v>-5400</v>
+      </c>
+      <c r="F24" s="3">
         <v>-2800</v>
       </c>
-      <c r="E24" s="3">
+      <c r="G24" s="3">
         <v>-4800</v>
       </c>
-      <c r="F24" s="3">
+      <c r="H24" s="3">
         <v>-31300</v>
       </c>
-      <c r="G24" s="3">
+      <c r="I24" s="3">
         <v>-17000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="J24" s="3">
         <v>1700</v>
       </c>
-      <c r="I24" s="3">
+      <c r="K24" s="3">
         <v>-11900</v>
       </c>
-      <c r="J24" s="3">
+      <c r="L24" s="3">
         <v>-26100</v>
       </c>
-      <c r="K24" s="3">
+      <c r="M24" s="3">
         <v>-24500</v>
       </c>
-      <c r="L24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1336,84 +1433,102 @@
       <c r="N25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O25" s="3">
+        <v>0</v>
+      </c>
+      <c r="P25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-50400</v>
+      </c>
+      <c r="E26" s="3">
+        <v>-74700</v>
+      </c>
+      <c r="F26" s="3">
         <v>-36200</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>-36000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>-10600</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>-187300</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>-80100</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>-59400</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>-87100</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>-89200</v>
       </c>
-      <c r="L26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-50400</v>
+      </c>
+      <c r="E27" s="3">
+        <v>-74700</v>
+      </c>
+      <c r="F27" s="3">
         <v>-36200</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>-36000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>-10600</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>-211100</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>-372200</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>-221500</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>-245800</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>-240800</v>
       </c>
-      <c r="L27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1450,8 +1565,14 @@
       <c r="N28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O28" s="3">
+        <v>0</v>
+      </c>
+      <c r="P28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1488,8 +1609,14 @@
       <c r="N29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O29" s="3">
+        <v>0</v>
+      </c>
+      <c r="P29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1526,8 +1653,14 @@
       <c r="N30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O30" s="3">
+        <v>0</v>
+      </c>
+      <c r="P30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1564,8 +1697,14 @@
       <c r="N31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O31" s="3">
+        <v>0</v>
+      </c>
+      <c r="P31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1573,75 +1712,87 @@
         <v>-1300</v>
       </c>
       <c r="E32" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="F32" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="G32" s="3">
         <v>-1400</v>
       </c>
-      <c r="F32" s="3">
+      <c r="H32" s="3">
         <v>-1700</v>
       </c>
-      <c r="G32" s="3">
+      <c r="I32" s="3">
         <v>-200</v>
       </c>
-      <c r="H32" s="3">
+      <c r="J32" s="3">
         <v>-2200</v>
       </c>
-      <c r="I32" s="3">
+      <c r="K32" s="3">
         <v>-900</v>
       </c>
-      <c r="J32" s="3">
+      <c r="L32" s="3">
         <v>-1100</v>
       </c>
-      <c r="K32" s="3">
+      <c r="M32" s="3">
         <v>-1200</v>
       </c>
-      <c r="L32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-50400</v>
+      </c>
+      <c r="E33" s="3">
+        <v>-74700</v>
+      </c>
+      <c r="F33" s="3">
         <v>-36200</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>-36000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>-10600</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>-187300</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>-80100</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>-59400</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>-87100</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>-89200</v>
       </c>
-      <c r="L33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1678,89 +1829,107 @@
       <c r="N34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O34" s="3">
+        <v>0</v>
+      </c>
+      <c r="P34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-50400</v>
+      </c>
+      <c r="E35" s="3">
+        <v>-74700</v>
+      </c>
+      <c r="F35" s="3">
         <v>-36200</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>-36000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>-10600</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>-187300</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>-80100</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>-59400</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>-87100</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>-89200</v>
       </c>
-      <c r="L35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46234</v>
+      </c>
+      <c r="E38" s="2">
+        <v>46142</v>
+      </c>
+      <c r="F38" s="2">
         <v>46053</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45961</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45869</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45777</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45688</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45596</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>45504</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>45412</v>
       </c>
-      <c r="L38" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="M38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="N38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="P38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1775,8 +1944,10 @@
       <c r="L39" s="3"/>
       <c r="M39" s="3"/>
       <c r="N39" s="3"/>
-    </row>
-    <row r="40" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O39" s="3"/>
+      <c r="P39" s="3"/>
+    </row>
+    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1791,35 +1962,37 @@
       <c r="L40" s="3"/>
       <c r="M40" s="3"/>
       <c r="N40" s="3"/>
-    </row>
-    <row r="41" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O40" s="3"/>
+      <c r="P40" s="3"/>
+    </row>
+    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>309900</v>
+      </c>
+      <c r="E41" s="3">
+        <v>390800</v>
+      </c>
+      <c r="F41" s="3">
         <v>358100</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>298100</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>271100</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>228100</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>121300</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>68200</v>
       </c>
-      <c r="J41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L41" s="3" t="s">
         <v>3</v>
       </c>
@@ -1829,8 +2002,14 @@
       <c r="N41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -1867,35 +2046,41 @@
       <c r="N42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O42" s="3">
+        <v>0</v>
+      </c>
+      <c r="P42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>353500</v>
+      </c>
+      <c r="E43" s="3">
+        <v>330500</v>
+      </c>
+      <c r="F43" s="3">
         <v>407800</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>284800</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>265700</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>249100</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>314700</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>267500</v>
       </c>
-      <c r="J43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L43" s="3" t="s">
         <v>3</v>
       </c>
@@ -1905,8 +2090,14 @@
       <c r="N43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -1943,35 +2134,41 @@
       <c r="N44" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="45" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P44" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>71000</v>
+      </c>
+      <c r="E45" s="3">
+        <v>61100</v>
+      </c>
+      <c r="F45" s="3">
         <v>54800</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>50400</v>
       </c>
-      <c r="F45" s="3">
+      <c r="H45" s="3">
         <v>45700</v>
       </c>
-      <c r="G45" s="3">
+      <c r="I45" s="3">
         <v>42300</v>
       </c>
-      <c r="H45" s="3">
+      <c r="J45" s="3">
         <v>49300</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>36300</v>
       </c>
-      <c r="J45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L45" s="3" t="s">
         <v>3</v>
       </c>
@@ -1981,35 +2178,41 @@
       <c r="N45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>776700</v>
+      </c>
+      <c r="E46" s="3">
+        <v>823300</v>
+      </c>
+      <c r="F46" s="3">
         <v>850700</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>669500</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>626600</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>556600</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>512400</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>398000</v>
       </c>
-      <c r="J46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2019,8 +2222,14 @@
       <c r="N46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2057,35 +2266,41 @@
       <c r="N47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>66200</v>
+      </c>
+      <c r="E48" s="3">
+        <v>55900</v>
+      </c>
+      <c r="F48" s="3">
         <v>52100</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>48300</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>46500</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>45300</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>44500</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>45800</v>
       </c>
-      <c r="J48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2095,46 +2310,58 @@
       <c r="N48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>6547100</v>
+      </c>
+      <c r="E49" s="3">
+        <v>6478200</v>
+      </c>
+      <c r="F49" s="3">
         <v>6529000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
         <v>6580200</v>
       </c>
-      <c r="F49" s="3">
+      <c r="H49" s="3">
         <v>6612300</v>
       </c>
-      <c r="G49" s="3">
+      <c r="I49" s="3">
         <v>6662500</v>
       </c>
-      <c r="H49" s="3">
+      <c r="J49" s="3">
         <v>6712400</v>
       </c>
-      <c r="I49" s="3">
+      <c r="K49" s="3">
         <v>6743000</v>
       </c>
-      <c r="J49" s="3">
-        <v>0</v>
-      </c>
-      <c r="K49" s="3">
-        <v>0</v>
-      </c>
-      <c r="L49" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M49" s="3" t="s">
-        <v>3</v>
+      <c r="L49" s="3">
+        <v>0</v>
+      </c>
+      <c r="M49" s="3">
+        <v>0</v>
       </c>
       <c r="N49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2171,8 +2398,14 @@
       <c r="N50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O50" s="3">
+        <v>0</v>
+      </c>
+      <c r="P50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2209,35 +2442,41 @@
       <c r="N51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O51" s="3">
+        <v>0</v>
+      </c>
+      <c r="P51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>7800</v>
+      </c>
+      <c r="E52" s="3">
+        <v>6400</v>
+      </c>
+      <c r="F52" s="3">
         <v>6200</v>
       </c>
-      <c r="E52" s="3">
+      <c r="G52" s="3">
         <v>6900</v>
       </c>
-      <c r="F52" s="3">
+      <c r="H52" s="3">
         <v>7100</v>
       </c>
-      <c r="G52" s="3">
+      <c r="I52" s="3">
         <v>6200</v>
       </c>
-      <c r="H52" s="3">
+      <c r="J52" s="3">
         <v>6400</v>
       </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>12000</v>
       </c>
-      <c r="J52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L52" s="3" t="s">
         <v>3</v>
       </c>
@@ -2247,8 +2486,14 @@
       <c r="N52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2285,35 +2530,41 @@
       <c r="N53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O53" s="3">
+        <v>0</v>
+      </c>
+      <c r="P53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>7583800</v>
+      </c>
+      <c r="E54" s="3">
+        <v>7525900</v>
+      </c>
+      <c r="F54" s="3">
         <v>7597600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>7474800</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>7445900</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>7414500</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>7411900</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>7316500</v>
       </c>
-      <c r="J54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L54" s="3" t="s">
         <v>3</v>
       </c>
@@ -2323,8 +2574,14 @@
       <c r="N54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2339,8 +2596,10 @@
       <c r="L55" s="3"/>
       <c r="M55" s="3"/>
       <c r="N55" s="3"/>
-    </row>
-    <row r="56" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O55" s="3"/>
+      <c r="P55" s="3"/>
+    </row>
+    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2355,35 +2614,37 @@
       <c r="L56" s="3"/>
       <c r="M56" s="3"/>
       <c r="N56" s="3"/>
-    </row>
-    <row r="57" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O56" s="3"/>
+      <c r="P56" s="3"/>
+    </row>
+    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>13400</v>
+      </c>
+      <c r="E57" s="3">
+        <v>13500</v>
+      </c>
+      <c r="F57" s="3">
         <v>5800</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>4200</v>
-      </c>
-      <c r="F57" s="3">
-        <v>3500</v>
-      </c>
-      <c r="G57" s="3">
-        <v>3800</v>
       </c>
       <c r="H57" s="3">
         <v>3500</v>
       </c>
       <c r="I57" s="3">
+        <v>3800</v>
+      </c>
+      <c r="J57" s="3">
+        <v>3500</v>
+      </c>
+      <c r="K57" s="3">
         <v>12100</v>
       </c>
-      <c r="J57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L57" s="3" t="s">
         <v>3</v>
       </c>
@@ -2393,73 +2654,85 @@
       <c r="N57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>5900</v>
+      </c>
+      <c r="E58" s="3">
+        <v>5400</v>
+      </c>
+      <c r="F58" s="3">
         <v>5300</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>5200</v>
       </c>
-      <c r="F58" s="3">
+      <c r="H58" s="3">
         <v>5000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="I58" s="3">
         <v>4900</v>
       </c>
-      <c r="H58" s="3">
+      <c r="J58" s="3">
         <v>4600</v>
       </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>4300</v>
       </c>
-      <c r="J58" s="3">
-        <v>0</v>
-      </c>
-      <c r="K58" s="3">
-        <v>0</v>
-      </c>
-      <c r="L58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M58" s="3" t="s">
-        <v>3</v>
+      <c r="L58" s="3">
+        <v>0</v>
+      </c>
+      <c r="M58" s="3">
+        <v>0</v>
       </c>
       <c r="N58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>545900</v>
+      </c>
+      <c r="E59" s="3">
+        <v>529900</v>
+      </c>
+      <c r="F59" s="3">
         <v>548600</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>454400</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>451000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>437800</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>448300</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>370900</v>
       </c>
-      <c r="J59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L59" s="3" t="s">
         <v>3</v>
       </c>
@@ -2469,35 +2742,41 @@
       <c r="N59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>632600</v>
+      </c>
+      <c r="E60" s="3">
+        <v>590300</v>
+      </c>
+      <c r="F60" s="3">
         <v>643300</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>525100</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>504500</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>474900</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>574700</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>484400</v>
       </c>
-      <c r="J60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L60" s="3" t="s">
         <v>3</v>
       </c>
@@ -2507,35 +2786,41 @@
       <c r="N60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>25500</v>
+      </c>
+      <c r="E61" s="3">
+        <v>13600</v>
+      </c>
+      <c r="F61" s="3">
         <v>12700</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>14100</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>15400</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>16700</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>1042300</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>1584300</v>
       </c>
-      <c r="J61" s="3">
-        <v>0</v>
-      </c>
-      <c r="K61" s="3">
-        <v>0</v>
-      </c>
       <c r="L61" s="3">
         <v>0</v>
       </c>
@@ -2545,8 +2830,14 @@
       <c r="N61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O61" s="3">
+        <v>0</v>
+      </c>
+      <c r="P61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -2562,18 +2853,18 @@
       <c r="G62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H62" s="3">
+      <c r="H62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J62" s="3">
         <v>11210400</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>1884700</v>
       </c>
-      <c r="J62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L62" s="3" t="s">
         <v>3</v>
       </c>
@@ -2583,8 +2874,14 @@
       <c r="N62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2621,8 +2918,14 @@
       <c r="N63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O63" s="3">
+        <v>0</v>
+      </c>
+      <c r="P63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2659,8 +2962,14 @@
       <c r="N64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O64" s="3">
+        <v>0</v>
+      </c>
+      <c r="P64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2697,35 +3006,41 @@
       <c r="N65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O65" s="3">
+        <v>0</v>
+      </c>
+      <c r="P65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>722200</v>
+      </c>
+      <c r="E66" s="3">
+        <v>683700</v>
+      </c>
+      <c r="F66" s="3">
         <v>751300</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>645200</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>629800</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>636700</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>13000400</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>4113600</v>
       </c>
-      <c r="J66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L66" s="3" t="s">
         <v>3</v>
       </c>
@@ -2735,8 +3050,14 @@
       <c r="N66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2751,8 +3072,10 @@
       <c r="L67" s="3"/>
       <c r="M67" s="3"/>
       <c r="N67" s="3"/>
-    </row>
-    <row r="68" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O67" s="3"/>
+      <c r="P67" s="3"/>
+    </row>
+    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2789,8 +3112,14 @@
       <c r="N68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O68" s="3">
+        <v>0</v>
+      </c>
+      <c r="P68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2827,8 +3156,14 @@
       <c r="N69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O69" s="3">
+        <v>0</v>
+      </c>
+      <c r="P69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2848,25 +3183,31 @@
         <v>0</v>
       </c>
       <c r="I70" s="3">
+        <v>0</v>
+      </c>
+      <c r="J70" s="3">
+        <v>0</v>
+      </c>
+      <c r="K70" s="3">
         <v>3957000</v>
       </c>
-      <c r="J70" s="3">
-        <v>0</v>
-      </c>
-      <c r="K70" s="3">
+      <c r="L70" s="3">
+        <v>0</v>
+      </c>
+      <c r="M70" s="3">
         <v>3960200</v>
       </c>
-      <c r="L70" s="3">
-        <v>0</v>
-      </c>
-      <c r="M70" s="3">
-        <v>0</v>
-      </c>
       <c r="N70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O70" s="3">
+        <v>0</v>
+      </c>
+      <c r="P70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2903,35 +3244,41 @@
       <c r="N71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O71" s="3">
+        <v>0</v>
+      </c>
+      <c r="P71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-375800</v>
+      </c>
+      <c r="E72" s="3">
+        <v>-325500</v>
+      </c>
+      <c r="F72" s="3">
         <v>-250800</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>-214600</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>-178600</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>-168100</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>-5588400</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>-814400</v>
       </c>
-      <c r="J72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L72" s="3" t="s">
         <v>3</v>
       </c>
@@ -2941,8 +3288,14 @@
       <c r="N72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2979,8 +3332,14 @@
       <c r="N73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O73" s="3">
+        <v>0</v>
+      </c>
+      <c r="P73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3017,8 +3376,14 @@
       <c r="N74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O74" s="3">
+        <v>0</v>
+      </c>
+      <c r="P74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3055,46 +3420,58 @@
       <c r="N75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O75" s="3">
+        <v>0</v>
+      </c>
+      <c r="P75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>6861600</v>
+      </c>
+      <c r="E76" s="3">
+        <v>6842200</v>
+      </c>
+      <c r="F76" s="3">
         <v>6846200</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>6829600</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>6816100</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>6777800</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>-5588400</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>-754100</v>
       </c>
-      <c r="J76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M76" s="3">
         <v>-541200</v>
       </c>
-      <c r="L76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3131,89 +3508,107 @@
       <c r="N77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O77" s="3">
+        <v>0</v>
+      </c>
+      <c r="P77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46234</v>
+      </c>
+      <c r="E80" s="2">
+        <v>46142</v>
+      </c>
+      <c r="F80" s="2">
         <v>46053</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45961</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45869</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45777</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45688</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45596</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>45504</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>45412</v>
       </c>
-      <c r="L80" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="M80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="N80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="P80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-50400</v>
+      </c>
+      <c r="E81" s="3">
+        <v>-74700</v>
+      </c>
+      <c r="F81" s="3">
         <v>-36200</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>-36000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>-10600</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>-187300</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>-80100</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>-59400</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>-87100</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>-89200</v>
       </c>
-      <c r="L81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3228,31 +3623,33 @@
       <c r="L82" s="3"/>
       <c r="M82" s="3"/>
       <c r="N82" s="3"/>
-    </row>
-    <row r="83" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O82" s="3"/>
+      <c r="P82" s="3"/>
+    </row>
+    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>1600</v>
+        <v>1900</v>
       </c>
       <c r="E83" s="3">
-        <v>1700</v>
+        <v>1900</v>
       </c>
       <c r="F83" s="3">
         <v>1600</v>
       </c>
       <c r="G83" s="3">
-        <v>1600</v>
+        <v>1700</v>
       </c>
       <c r="H83" s="3">
         <v>1600</v>
       </c>
-      <c r="I83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J83" s="3" t="s">
-        <v>3</v>
+      <c r="I83" s="3">
+        <v>1600</v>
+      </c>
+      <c r="J83" s="3">
+        <v>1600</v>
       </c>
       <c r="K83" s="3" t="s">
         <v>3</v>
@@ -3266,8 +3663,14 @@
       <c r="N83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3304,8 +3707,14 @@
       <c r="N84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O84" s="3">
+        <v>0</v>
+      </c>
+      <c r="P84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3342,8 +3751,14 @@
       <c r="N85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O85" s="3">
+        <v>0</v>
+      </c>
+      <c r="P85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3380,8 +3795,14 @@
       <c r="N86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O86" s="3">
+        <v>0</v>
+      </c>
+      <c r="P86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3418,8 +3839,14 @@
       <c r="N87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O87" s="3">
+        <v>0</v>
+      </c>
+      <c r="P87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3456,46 +3883,58 @@
       <c r="N88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O88" s="3">
+        <v>0</v>
+      </c>
+      <c r="P88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>45000</v>
+      </c>
+      <c r="E89" s="3">
+        <v>38200</v>
+      </c>
+      <c r="F89" s="3">
         <v>63900</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>53600</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>49900</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>-96800</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>13800</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>-12000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>-52800</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>-55400</v>
       </c>
-      <c r="L89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3510,46 +3949,54 @@
       <c r="L90" s="3"/>
       <c r="M90" s="3"/>
       <c r="N90" s="3"/>
-    </row>
-    <row r="91" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O90" s="3"/>
+      <c r="P90" s="3"/>
+    </row>
+    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="E91" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="F91" s="3">
         <v>-2300</v>
       </c>
-      <c r="E91" s="3">
+      <c r="G91" s="3">
         <v>-17300</v>
       </c>
-      <c r="F91" s="3">
+      <c r="H91" s="3">
         <v>-1000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="I91" s="3">
         <v>-2200</v>
       </c>
-      <c r="H91" s="3">
+      <c r="J91" s="3">
         <v>-1500</v>
       </c>
-      <c r="I91" s="3">
+      <c r="K91" s="3">
         <v>-2300</v>
       </c>
-      <c r="J91" s="3">
+      <c r="L91" s="3">
         <v>-900</v>
       </c>
-      <c r="K91" s="3">
+      <c r="M91" s="3">
         <v>-600</v>
       </c>
-      <c r="L91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3586,8 +4033,14 @@
       <c r="N92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O92" s="3">
+        <v>0</v>
+      </c>
+      <c r="P92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3624,46 +4077,58 @@
       <c r="N93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O93" s="3">
+        <v>0</v>
+      </c>
+      <c r="P93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-125800</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-5700</v>
+      </c>
+      <c r="F94" s="3">
         <v>-6900</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>-20800</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>-4000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>-3900</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>-12700</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>-4800</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>-3800</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>-7700</v>
       </c>
-      <c r="L94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3678,8 +4143,10 @@
       <c r="L95" s="3"/>
       <c r="M95" s="3"/>
       <c r="N95" s="3"/>
-    </row>
-    <row r="96" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O95" s="3"/>
+      <c r="P95" s="3"/>
+    </row>
+    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -3716,8 +4183,14 @@
       <c r="N96" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="97" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P96" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3754,8 +4227,14 @@
       <c r="N97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O97" s="3">
+        <v>0</v>
+      </c>
+      <c r="P97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3792,8 +4271,14 @@
       <c r="N98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O98" s="3">
+        <v>0</v>
+      </c>
+      <c r="P98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3830,46 +4315,58 @@
       <c r="N99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O99" s="3">
+        <v>0</v>
+      </c>
+      <c r="P99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3">
-        <v>0</v>
-      </c>
-      <c r="E100" s="3">
+      <c r="D100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F100" s="3">
+        <v>0</v>
+      </c>
+      <c r="G100" s="3">
         <v>-5700</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>-3000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>210600</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>48200</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>-4700</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>-400</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>-1800</v>
       </c>
-      <c r="L100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -3906,42 +4403,54 @@
       <c r="N101" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="102" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-80800</v>
+      </c>
+      <c r="E102" s="3">
+        <v>32500</v>
+      </c>
+      <c r="F102" s="3">
         <v>57000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>27100</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>43000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>109900</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>49300</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>-21500</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>-57000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>-64900</v>
       </c>
-      <c r="L102" s="3">
-        <v>0</v>
-      </c>
-      <c r="M102" s="3">
-        <v>0</v>
-      </c>
       <c r="N102" s="3">
+        <v>0</v>
+      </c>
+      <c r="O102" s="3">
+        <v>0</v>
+      </c>
+      <c r="P102" s="3">
         <v>0</v>
       </c>
     </row>
